--- a/РАБОЧИЙ СТОЛ/расчеты Останкино СЫРЫ/Донецк/дв 25,08,26 днрсч ост сыр.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино СЫРЫ/Донецк/дв 25,08,26 днрсч ост сыр.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\08,26\25,08,26 Останкино СЫРЫ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\Создание расчетов\ПОКОМ_КИ_UK_Sch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC8504D-8250-4B4B-BBA5-232738B42EB1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6FE605-CE0B-435A-94FF-1ADE3BDC4D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,20 +20,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AH$49</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="93">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -313,63 +305,6 @@
   <si>
     <t>27,08,26 - нет на заводе / 24,08,26 - нет на заводе / 13,08,26 - нет на заводе / 30,07,26 - нет на заводе / 62шт в уценку (28,07,26)</t>
   </si>
-  <si>
-    <t>07,8,06/ % 200нет на заводе / ,8,06 - нет на заводе / 03,8,06 - нет на заводе / 3,7,06 - нет на заводе / 60шт 5 уценку (08,7,06)</t>
-  </si>
-  <si>
-    <t>97,168,96  45% " ветчиной" нет на заводе / 8,168,96 - нет на заводе / 63,168,96 - нет на заводе / 316,167,96 - нет на заводе / 69шт в уценку (98,167,96)</t>
-  </si>
-  <si>
-    <t>107,8,106  45%" грибами" нет на заводе / 14,8,106 - нет на заводе / 63,8,106 - нет на заводе / 3,7,106 - нет на заводе / 610шт С уценку (108,7,106)</t>
-  </si>
-  <si>
-    <t>577,2908,576 "" нет на заводе / 49,2908,576 - нет на заводе / 353,2908,576 - нет на заводе / 3290,2907,576 - нет на заводе / 657шт м уценку (578,2907,576)</t>
-  </si>
-  <si>
-    <t>197,1208,196 ,5 % 180 нет на заводе / ,1208,196 - нет на заводе / 113,1208,196 - нет на заводе / 3120,1207,196 - нет на заводе / 619шт г уценку (198,1207,196)</t>
-  </si>
-  <si>
-    <t>17,288,16   % нет на заводе / 8,288,16 - нет на заводе / 13,288,16 - нет на заводе / 328,287,16 - нет на заводе / 61шт С уценку (18,287,16)</t>
-  </si>
-  <si>
-    <t>67,1688,66 "% нет на заводе / ,1688,66 - нет на заводе / 83,1688,66 - нет на заводе / 3168,1687,66 - нет на заводе / 66шт к уценку (68,1687,66)</t>
-  </si>
-  <si>
-    <t>57,8,56  /8нет на заводе / 184,8,56 - нет на заводе / 123,8,56 - нет на заводе / 3,7,56 - нет на заводе / 65шт 1 уценку (58,7,56)</t>
-  </si>
-  <si>
-    <t>187,968,186  % 100нет на заводе / ,968,186 - нет на заводе / 133,968,186 - нет на заводе / 396,967,186 - нет на заводе / 618шт 1 уценку (188,967,186)</t>
-  </si>
-  <si>
-    <t>517,3808,516  ""  гр (10нет на заводе / ,3808,516 - нет на заводе / 253,3808,516 - нет на заводе / 3380,3807,516 - нет на заводе / 651шт 1 уценку (518,3807,516)</t>
-  </si>
-  <si>
-    <t>507,3308,506  "" г нет на заводе / ,3308,506 - нет на заводе / 483,3308,506 - нет на заводе / 3330,3307,506 - нет на заводе / 650шт % уценку (508,3307,506)</t>
-  </si>
-  <si>
-    <t>97,8,96  "    нет на заводе / 68,8,96 - нет на заводе / 73,8,96 - нет на заводе / 3,7,96 - нет на заводе / 69шт в уценку (98,7,96)</t>
-  </si>
-  <si>
-    <t>97,328,96  % 180 нет на заводе / 30,328,96 - нет на заводе / 63,328,96 - нет на заводе / 332,327,96 - нет на заводе / 69шт П уценку (98,327,96)</t>
-  </si>
-  <si>
-    <t>47,8,46 "    нет на заводе / ,8,46 - нет на заводе / 13,8,46 - нет на заводе / 3,7,46 - нет на заводе / 64кг п уценку (48,7,46)</t>
-  </si>
-  <si>
-    <t>107,668,106 ",     нет на заводе / ,668,106 - нет на заводе / 33,668,106 - нет на заводе / 366,667,106 - нет на заводе / 610кг с уценку (108,667,106)</t>
-  </si>
-  <si>
-    <t>417,4748,416  % 100 нет на заводе / ,4748,416 - нет на заводе / 203,4748,416 - нет на заводе / 3474,4747,416 - нет на заводе / 641шт 4 уценку (418,4747,416)</t>
-  </si>
-  <si>
-    <t>387,8,386   нет на заводе / ,8,386 - нет на заводе / 443,8,386 - нет на заводе / 3,7,386 - нет на заводе / 638шт 4 уценку (388,7,386)</t>
-  </si>
-  <si>
-    <t>167,648,166  нет на заводе / ,648,166 - нет на заводе / 93,648,166 - нет на заводе / 364,647,166 - нет на заводе / 616шт С уценку (168,647,166)</t>
-  </si>
-  <si>
-    <t>117,8,116/ % 200нет на заводе / ,8,116 - нет на заводе / 93,8,116 - нет на заводе / 3,7,116 - нет на заводе / 611шт 2 уценку (118,7,116)</t>
-  </si>
 </sst>
 </file>
 
@@ -487,7 +422,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -501,11 +436,8 @@
     <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1304,7 +1236,7 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
-      <c r="T6" s="16"/>
+      <c r="T6" s="1"/>
       <c r="U6" s="1">
         <f>(F6+O6+Q6)/P6</f>
         <v>26.5625</v>
@@ -1420,7 +1352,7 @@
         <v>24</v>
       </c>
       <c r="S7" s="5"/>
-      <c r="T7" s="16"/>
+      <c r="T7" s="1"/>
       <c r="U7" s="1">
         <f t="shared" ref="U7:U49" si="7">(F7+O7+Q7)/P7</f>
         <v>15</v>
@@ -1459,7 +1391,7 @@
       <c r="AF7" s="1">
         <v>0</v>
       </c>
-      <c r="AG7" s="15" t="s">
+      <c r="AG7" s="14" t="s">
         <v>85</v>
       </c>
       <c r="AH7" s="1">
@@ -1536,7 +1468,7 @@
         <v>24</v>
       </c>
       <c r="S8" s="5"/>
-      <c r="T8" s="16"/>
+      <c r="T8" s="1"/>
       <c r="U8" s="1">
         <f t="shared" si="7"/>
         <v>15</v>
@@ -1575,7 +1507,7 @@
       <c r="AF8" s="1">
         <v>0</v>
       </c>
-      <c r="AG8" s="15" t="s">
+      <c r="AG8" s="14" t="s">
         <v>85</v>
       </c>
       <c r="AH8" s="1">
@@ -1652,7 +1584,7 @@
         <v>30</v>
       </c>
       <c r="S9" s="5"/>
-      <c r="T9" s="16"/>
+      <c r="T9" s="1"/>
       <c r="U9" s="1">
         <f t="shared" si="7"/>
         <v>14.999999999999998</v>
@@ -1717,7 +1649,7 @@
       <c r="AX9" s="1"/>
     </row>
     <row r="10" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1754,11 +1686,11 @@
       <c r="Q10" s="5">
         <v>24</v>
       </c>
-      <c r="R10" s="18">
+      <c r="R10" s="15">
         <v>0</v>
       </c>
       <c r="S10" s="5"/>
-      <c r="T10" s="16"/>
+      <c r="T10" s="1"/>
       <c r="U10" s="1" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -1825,7 +1757,7 @@
       <c r="AX10" s="1"/>
     </row>
     <row r="11" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1862,11 +1794,11 @@
       <c r="Q11" s="5">
         <v>24</v>
       </c>
-      <c r="R11" s="18">
+      <c r="R11" s="15">
         <v>0</v>
       </c>
       <c r="S11" s="5"/>
-      <c r="T11" s="16"/>
+      <c r="T11" s="1"/>
       <c r="U11" s="1" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -1974,7 +1906,7 @@
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
       <c r="S12" s="5"/>
-      <c r="T12" s="16"/>
+      <c r="T12" s="1"/>
       <c r="U12" s="1">
         <f t="shared" si="7"/>
         <v>136.73052763819095</v>
@@ -2013,7 +1945,7 @@
       <c r="AF12" s="1">
         <v>2.6175999999999999</v>
       </c>
-      <c r="AG12" s="14" t="s">
+      <c r="AG12" s="13" t="s">
         <v>44</v>
       </c>
       <c r="AH12" s="1">
@@ -2082,7 +2014,7 @@
       <c r="Q13" s="5"/>
       <c r="R13" s="5"/>
       <c r="S13" s="5"/>
-      <c r="T13" s="16"/>
+      <c r="T13" s="1"/>
       <c r="U13" s="1">
         <f t="shared" si="7"/>
         <v>350</v>
@@ -2121,7 +2053,7 @@
       <c r="AF13" s="1">
         <v>0.2</v>
       </c>
-      <c r="AG13" s="14" t="s">
+      <c r="AG13" s="13" t="s">
         <v>44</v>
       </c>
       <c r="AH13" s="1">
@@ -2195,7 +2127,7 @@
         <f>VLOOKUP(A14,'заказ сети'!A:B,2,0)</f>
         <v>48</v>
       </c>
-      <c r="T14" s="16">
+      <c r="T14" s="1">
         <v>50</v>
       </c>
       <c r="U14" s="1">
@@ -2236,7 +2168,7 @@
       <c r="AF14" s="1">
         <v>10.4</v>
       </c>
-      <c r="AG14" s="14" t="s">
+      <c r="AG14" s="13" t="s">
         <v>44</v>
       </c>
       <c r="AH14" s="1">
@@ -2307,7 +2239,7 @@
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
       <c r="S15" s="5"/>
-      <c r="T15" s="16"/>
+      <c r="T15" s="1"/>
       <c r="U15" s="1">
         <f t="shared" si="7"/>
         <v>43.939393939393945</v>
@@ -2346,7 +2278,7 @@
       <c r="AF15" s="1">
         <v>2.4</v>
       </c>
-      <c r="AG15" s="14" t="s">
+      <c r="AG15" s="13" t="s">
         <v>44</v>
       </c>
       <c r="AH15" s="1">
@@ -2420,7 +2352,7 @@
         <f>VLOOKUP(A16,'заказ сети'!A:B,2,0)</f>
         <v>144</v>
       </c>
-      <c r="T16" s="16">
+      <c r="T16" s="1">
         <v>150</v>
       </c>
       <c r="U16" s="1">
@@ -2461,7 +2393,7 @@
       <c r="AF16" s="1">
         <v>17</v>
       </c>
-      <c r="AG16" s="14" t="s">
+      <c r="AG16" s="13" t="s">
         <v>44</v>
       </c>
       <c r="AH16" s="1">
@@ -2540,7 +2472,7 @@
         <v>96</v>
       </c>
       <c r="S17" s="5"/>
-      <c r="T17" s="16"/>
+      <c r="T17" s="1"/>
       <c r="U17" s="1">
         <f t="shared" si="7"/>
         <v>10</v>
@@ -2657,7 +2589,7 @@
         <v>16</v>
       </c>
       <c r="S18" s="5"/>
-      <c r="T18" s="16"/>
+      <c r="T18" s="1"/>
       <c r="U18" s="1">
         <f t="shared" si="7"/>
         <v>15.689655172413794</v>
@@ -2771,7 +2703,7 @@
         <v>16</v>
       </c>
       <c r="S19" s="5"/>
-      <c r="T19" s="16"/>
+      <c r="T19" s="1"/>
       <c r="U19" s="1">
         <f t="shared" si="7"/>
         <v>15</v>
@@ -2887,7 +2819,7 @@
         <v>50</v>
       </c>
       <c r="S20" s="5"/>
-      <c r="T20" s="16"/>
+      <c r="T20" s="1"/>
       <c r="U20" s="1">
         <f t="shared" si="7"/>
         <v>15</v>
@@ -2997,7 +2929,7 @@
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
       <c r="S21" s="5"/>
-      <c r="T21" s="16"/>
+      <c r="T21" s="1"/>
       <c r="U21" s="1">
         <f t="shared" si="7"/>
         <v>23</v>
@@ -3101,7 +3033,7 @@
       <c r="Q22" s="5"/>
       <c r="R22" s="5"/>
       <c r="S22" s="5"/>
-      <c r="T22" s="16"/>
+      <c r="T22" s="1"/>
       <c r="U22" s="1" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -3140,7 +3072,7 @@
       <c r="AF22" s="1">
         <v>1.6</v>
       </c>
-      <c r="AG22" s="14" t="s">
+      <c r="AG22" s="13" t="s">
         <v>44</v>
       </c>
       <c r="AH22" s="1">
@@ -3216,7 +3148,7 @@
         <v>28</v>
       </c>
       <c r="S23" s="5"/>
-      <c r="T23" s="16"/>
+      <c r="T23" s="1"/>
       <c r="U23" s="1">
         <f t="shared" si="7"/>
         <v>18</v>
@@ -3329,7 +3261,7 @@
         <f>VLOOKUP(A24,'заказ сети'!A:B,2,0)</f>
         <v>132</v>
       </c>
-      <c r="T24" s="16">
+      <c r="T24" s="1">
         <v>130</v>
       </c>
       <c r="U24" s="1">
@@ -3439,7 +3371,7 @@
       <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
       <c r="S25" s="5"/>
-      <c r="T25" s="16"/>
+      <c r="T25" s="1"/>
       <c r="U25" s="1">
         <f t="shared" si="7"/>
         <v>29.246575342465754</v>
@@ -3555,7 +3487,7 @@
         <v>184</v>
       </c>
       <c r="S26" s="5"/>
-      <c r="T26" s="16"/>
+      <c r="T26" s="1"/>
       <c r="U26" s="1">
         <f t="shared" si="7"/>
         <v>15</v>
@@ -3665,7 +3597,7 @@
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
       <c r="S27" s="5"/>
-      <c r="T27" s="16"/>
+      <c r="T27" s="1"/>
       <c r="U27" s="1">
         <f t="shared" si="7"/>
         <v>21.964285714285715</v>
@@ -3775,7 +3707,7 @@
       <c r="Q28" s="5"/>
       <c r="R28" s="5"/>
       <c r="S28" s="5"/>
-      <c r="T28" s="16"/>
+      <c r="T28" s="1"/>
       <c r="U28" s="1">
         <f t="shared" si="7"/>
         <v>36.857142857142854</v>
@@ -3814,7 +3746,7 @@
       <c r="AF28" s="1">
         <v>12.2</v>
       </c>
-      <c r="AG28" s="14" t="s">
+      <c r="AG28" s="13" t="s">
         <v>44</v>
       </c>
       <c r="AH28" s="1">
@@ -3890,7 +3822,7 @@
         <f>VLOOKUP(A29,'заказ сети'!A:B,2,0)</f>
         <v>100</v>
       </c>
-      <c r="T29" s="16">
+      <c r="T29" s="1">
         <v>100</v>
       </c>
       <c r="U29" s="1">
@@ -4000,7 +3932,7 @@
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
-      <c r="T30" s="16"/>
+      <c r="T30" s="1"/>
       <c r="U30" s="1">
         <f t="shared" si="7"/>
         <v>38</v>
@@ -4039,7 +3971,7 @@
       <c r="AF30" s="1">
         <v>0.2</v>
       </c>
-      <c r="AG30" s="14" t="s">
+      <c r="AG30" s="13" t="s">
         <v>44</v>
       </c>
       <c r="AH30" s="1">
@@ -4110,7 +4042,7 @@
       <c r="Q31" s="5"/>
       <c r="R31" s="5"/>
       <c r="S31" s="5"/>
-      <c r="T31" s="16"/>
+      <c r="T31" s="1"/>
       <c r="U31" s="1">
         <f t="shared" si="7"/>
         <v>38.076923076923073</v>
@@ -4149,7 +4081,7 @@
       <c r="AF31" s="1">
         <v>1.8</v>
       </c>
-      <c r="AG31" s="14" t="s">
+      <c r="AG31" s="13" t="s">
         <v>44</v>
       </c>
       <c r="AH31" s="1">
@@ -4222,7 +4154,7 @@
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
       <c r="S32" s="5"/>
-      <c r="T32" s="16"/>
+      <c r="T32" s="1"/>
       <c r="U32" s="1">
         <f t="shared" si="7"/>
         <v>18.978494623655916</v>
@@ -4336,7 +4268,7 @@
         <v>70</v>
       </c>
       <c r="S33" s="5"/>
-      <c r="T33" s="16"/>
+      <c r="T33" s="1"/>
       <c r="U33" s="1">
         <f t="shared" si="7"/>
         <v>15</v>
@@ -4444,7 +4376,7 @@
       <c r="Q34" s="5"/>
       <c r="R34" s="5"/>
       <c r="S34" s="5"/>
-      <c r="T34" s="16"/>
+      <c r="T34" s="1"/>
       <c r="U34" s="1">
         <f t="shared" si="7"/>
         <v>34</v>
@@ -4483,7 +4415,7 @@
       <c r="AF34" s="1">
         <v>3</v>
       </c>
-      <c r="AG34" s="14" t="s">
+      <c r="AG34" s="13" t="s">
         <v>44</v>
       </c>
       <c r="AH34" s="1">
@@ -4562,7 +4494,7 @@
         <v>32</v>
       </c>
       <c r="S35" s="5"/>
-      <c r="T35" s="16"/>
+      <c r="T35" s="1"/>
       <c r="U35" s="1">
         <f t="shared" si="7"/>
         <v>15</v>
@@ -4670,7 +4602,7 @@
       <c r="Q36" s="5"/>
       <c r="R36" s="5"/>
       <c r="S36" s="5"/>
-      <c r="T36" s="16"/>
+      <c r="T36" s="1"/>
       <c r="U36" s="1">
         <f t="shared" si="7"/>
         <v>30.193080677576798</v>
@@ -4709,7 +4641,7 @@
       <c r="AF36" s="1">
         <v>1.3408</v>
       </c>
-      <c r="AG36" s="14" t="s">
+      <c r="AG36" s="13" t="s">
         <v>44</v>
       </c>
       <c r="AH36" s="1">
@@ -4780,7 +4712,7 @@
       <c r="Q37" s="5"/>
       <c r="R37" s="5"/>
       <c r="S37" s="5"/>
-      <c r="T37" s="16"/>
+      <c r="T37" s="1"/>
       <c r="U37" s="1">
         <f t="shared" si="7"/>
         <v>14.272396903144255</v>
@@ -4890,7 +4822,7 @@
       <c r="Q38" s="5"/>
       <c r="R38" s="5"/>
       <c r="S38" s="5"/>
-      <c r="T38" s="16"/>
+      <c r="T38" s="1"/>
       <c r="U38" s="1">
         <f t="shared" si="7"/>
         <v>19.298667653589934</v>
@@ -4996,7 +4928,7 @@
       <c r="Q39" s="5"/>
       <c r="R39" s="5"/>
       <c r="S39" s="5"/>
-      <c r="T39" s="16"/>
+      <c r="T39" s="1"/>
       <c r="U39" s="1">
         <f t="shared" si="7"/>
         <v>208.88258839226148</v>
@@ -5035,7 +4967,7 @@
       <c r="AF39" s="1">
         <v>0</v>
       </c>
-      <c r="AG39" s="14" t="s">
+      <c r="AG39" s="13" t="s">
         <v>44</v>
       </c>
       <c r="AH39" s="1">
@@ -5108,7 +5040,7 @@
       <c r="Q40" s="5"/>
       <c r="R40" s="5"/>
       <c r="S40" s="5"/>
-      <c r="T40" s="16"/>
+      <c r="T40" s="1"/>
       <c r="U40" s="1">
         <f t="shared" si="7"/>
         <v>14.94535519125683</v>
@@ -5216,7 +5148,7 @@
       <c r="Q41" s="5"/>
       <c r="R41" s="5"/>
       <c r="S41" s="5"/>
-      <c r="T41" s="16"/>
+      <c r="T41" s="1"/>
       <c r="U41" s="1">
         <f t="shared" si="7"/>
         <v>17.396449704142015</v>
@@ -5320,7 +5252,7 @@
       <c r="Q42" s="5"/>
       <c r="R42" s="5"/>
       <c r="S42" s="5"/>
-      <c r="T42" s="16"/>
+      <c r="T42" s="1"/>
       <c r="U42" s="1" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -5432,7 +5364,7 @@
       <c r="Q43" s="5"/>
       <c r="R43" s="5"/>
       <c r="S43" s="5"/>
-      <c r="T43" s="16"/>
+      <c r="T43" s="1"/>
       <c r="U43" s="1">
         <f t="shared" si="7"/>
         <v>19.761904761904763</v>
@@ -5540,7 +5472,7 @@
       <c r="Q44" s="5"/>
       <c r="R44" s="5"/>
       <c r="S44" s="5"/>
-      <c r="T44" s="16"/>
+      <c r="T44" s="1"/>
       <c r="U44" s="1">
         <f t="shared" si="7"/>
         <v>22.954545454545453</v>
@@ -5644,7 +5576,7 @@
       <c r="Q45" s="12"/>
       <c r="R45" s="5"/>
       <c r="S45" s="5"/>
-      <c r="T45" s="17"/>
+      <c r="T45" s="10"/>
       <c r="U45" s="10" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -5742,7 +5674,7 @@
       <c r="Q46" s="5"/>
       <c r="R46" s="5"/>
       <c r="S46" s="5"/>
-      <c r="T46" s="16"/>
+      <c r="T46" s="1"/>
       <c r="U46" s="1" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -5781,7 +5713,7 @@
       <c r="AF46" s="1">
         <v>0</v>
       </c>
-      <c r="AG46" s="14" t="s">
+      <c r="AG46" s="13" t="s">
         <v>44</v>
       </c>
       <c r="AH46" s="1">
@@ -5852,7 +5784,7 @@
       <c r="Q47" s="5"/>
       <c r="R47" s="5"/>
       <c r="S47" s="5"/>
-      <c r="T47" s="16"/>
+      <c r="T47" s="1"/>
       <c r="U47" s="1">
         <f t="shared" si="7"/>
         <v>28.18181818181818</v>
@@ -5891,7 +5823,7 @@
       <c r="AF47" s="1">
         <v>12.8</v>
       </c>
-      <c r="AG47" s="14" t="s">
+      <c r="AG47" s="13" t="s">
         <v>44</v>
       </c>
       <c r="AH47" s="1">
@@ -5958,7 +5890,7 @@
       <c r="Q48" s="12"/>
       <c r="R48" s="5"/>
       <c r="S48" s="5"/>
-      <c r="T48" s="17"/>
+      <c r="T48" s="10"/>
       <c r="U48" s="10" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
@@ -6060,7 +5992,7 @@
       <c r="Q49" s="5"/>
       <c r="R49" s="5"/>
       <c r="S49" s="5"/>
-      <c r="T49" s="16"/>
+      <c r="T49" s="1"/>
       <c r="U49" s="1">
         <f t="shared" si="7"/>
         <v>29.405713439905266</v>
@@ -6099,7 +6031,7 @@
       <c r="AF49" s="1">
         <v>7.7816000000000001</v>
       </c>
-      <c r="AG49" s="14" t="s">
+      <c r="AG49" s="13" t="s">
         <v>44</v>
       </c>
       <c r="AH49" s="1">
